--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -723,60 +723,64 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +794,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>2/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,43 +913,947 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>—/3</t>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -753,24 +753,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -862,36 +862,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -899,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -923,37 +919,33 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -991,24 +983,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1049,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1164,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1183,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1203,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1244,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1264,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1322,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1355,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,17 +1383,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1399,13 +1403,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1516,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1627,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1738,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1848,12 +1856,797 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,18 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +949,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1068,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1096,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,17 +1157,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1169,13 +1177,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1213,24 +1225,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1289,12 +1301,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1344,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1398,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1453,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1474,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1514,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1635,7 +1655,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1683,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1696,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1744,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1861,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1972,7 +2000,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2083,7 +2111,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2198,7 +2226,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2287,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2309,7 +2337,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2398,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2414,13 +2442,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2513,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2531,7 +2563,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2641,12 +2673,690 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,18 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,12 +1057,12 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1177,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1306,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1572,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1605,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,17 +1637,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1649,13 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1693,24 +1705,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1720,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1769,7 +1781,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1835,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1917,32 +1929,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1950,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1974,33 +1990,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2028,32 +2048,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2061,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2085,33 +2109,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2139,32 +2167,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2172,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2196,27 +2228,27 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2287,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2326,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2365,32 +2397,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2398,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2422,17 +2458,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2442,17 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2480,32 +2516,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2513,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2537,33 +2577,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2663,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2678,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2778,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2850,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2889,7 +2933,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2961,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3015,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3120,13 +3164,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3226,7 +3274,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3249,22 +3297,22 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3297,12 +3345,12 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3316,47 +3364,1185 @@
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>09:45</t>
         </is>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z25" s="2" t="inlineStr">
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
+      <c r="AA26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,18 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2607,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2894,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,32 +2976,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3005,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3029,37 +3037,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3087,32 +3095,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3120,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3144,17 +3156,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3164,17 +3176,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3289,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3317,32 +3329,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3350,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3374,37 +3390,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3432,32 +3448,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -3465,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3489,37 +3509,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3547,32 +3567,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3580,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3604,17 +3628,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3624,17 +3648,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3734,7 +3758,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3749,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3777,32 +3801,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -3810,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3834,33 +3862,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3960,7 +3992,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3975,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4190,7 +4222,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4205,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4431,7 +4463,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4546,6 +4578,811 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1176,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,14 +2477,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,18 +2826,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2937,18 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,7 +3060,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3067,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,17 +3299,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3420,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3539,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3892,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3920,32 +3928,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3953,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3977,17 +3989,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3997,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4047,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4068,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4092,17 +4108,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4112,17 +4128,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4150,32 +4166,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4183,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4207,17 +4227,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4227,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4265,32 +4285,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4298,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4322,33 +4346,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4376,32 +4404,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4409,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4433,17 +4465,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4453,17 +4485,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4491,32 +4523,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4524,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4548,33 +4584,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4689,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4789,7 +4829,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4804,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4905,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4919,7 +4959,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4980,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5024,17 +5064,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5134,7 +5174,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5149,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5250,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5254,17 +5294,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5365,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5379,7 +5419,693 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,14 +1057,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,14 +2243,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,17 +3065,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,14 +3651,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3771,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4642,32 +4642,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4675,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4699,17 +4703,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4719,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4757,32 +4761,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4790,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4814,17 +4822,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4834,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4872,32 +4880,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4905,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4929,17 +4941,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4949,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4987,32 +4999,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5020,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5044,17 +5060,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5064,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5217,32 +5233,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5250,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5274,17 +5294,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5294,12 +5314,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5365,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5404,7 +5424,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5447,32 +5467,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5480,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5504,17 +5528,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5524,12 +5548,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5595,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5634,7 +5658,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5710,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5754,17 +5778,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5960,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6105,7 +6129,467 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,17 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5352,32 +5352,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -5385,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5409,17 +5413,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5429,17 +5433,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5619,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5734,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5788,7 +5792,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5888,7 +5892,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5960,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6014,7 +6018,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6129,7 +6133,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6234,17 +6238,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,7 +6424,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6539,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6589,7 +6593,118 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,22 +3060,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,14 +3532,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,14 +4718,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -4733,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,22 +5190,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5481,24 +5481,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5590,32 +5590,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,17 +5651,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5667,17 +5671,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5705,32 +5709,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5738,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,37 +5770,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5820,32 +5828,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -5853,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5877,17 +5889,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5897,13 +5909,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5931,32 +5947,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5964,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5988,37 +6008,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6118,7 +6138,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6133,7 +6153,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6248,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6348,7 +6368,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6363,7 +6383,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6468,17 +6488,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6593,7 +6613,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6698,13 +6718,592 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,14 +4004,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,14 +4242,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,14 +5075,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,14 +5309,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,22 +5428,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5957,24 +5957,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6066,32 +6066,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6099,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,17 +6127,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6143,17 +6147,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6181,32 +6185,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -6214,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,37 +6246,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6296,32 +6304,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6329,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6353,17 +6365,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6373,12 +6385,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6411,32 +6423,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6444,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6468,17 +6484,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6488,17 +6504,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6526,32 +6542,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6559,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6583,37 +6603,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6641,32 +6661,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -6674,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6698,17 +6722,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6718,17 +6742,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6756,32 +6780,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6789,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6813,37 +6841,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6904,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6958,7 +6986,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7063,17 +7091,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7134,7 +7162,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7183,7 +7211,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7196,22 +7224,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7244,12 +7272,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7263,47 +7291,737 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
+      <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>82.3</t>
         </is>
       </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>3/15</t>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,22 +3060,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,22 +5075,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,22 +5785,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,22 +5904,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6142,17 +6142,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6552,24 +6552,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,22 +6737,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6790,24 +6790,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6899,32 +6899,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6932,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6956,37 +6960,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7014,32 +7018,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7047,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7071,32 +7079,32 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7162,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7201,7 +7209,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7244,32 +7252,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7277,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7301,37 +7313,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7359,32 +7371,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7392,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7416,17 +7432,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7436,12 +7452,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7507,7 +7523,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7546,7 +7562,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7561,7 +7577,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7638,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7671,12 +7687,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7791,7 +7807,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7914,22 +7930,22 @@
       <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -7962,12 +7978,12 @@
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8011,17 +8027,1167 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>86.8</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>12/15</t>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,22 +3060,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3179,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,22 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,22 +3651,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,22 +3885,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,22 +4361,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,22 +4718,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,17 +5314,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,22 +5428,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,22 +5666,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5785,22 +5785,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6261,22 +6261,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6380,22 +6380,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,22 +6499,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6618,22 +6618,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,22 +6975,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7381,12 +7381,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7447,22 +7447,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7490,32 +7490,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7523,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7547,17 +7551,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7567,17 +7571,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7605,32 +7609,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7638,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7662,37 +7670,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7720,32 +7728,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -7753,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7777,37 +7789,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7907,7 +7919,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7922,7 +7934,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7950,32 +7962,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7983,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8007,37 +8023,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8065,32 +8081,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -8098,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8122,37 +8142,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8252,7 +8272,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8295,32 +8315,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8328,7 +8352,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8352,37 +8376,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8467,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8558,7 +8582,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8612,7 +8636,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8697,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8788,7 +8812,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8903,7 +8927,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8957,7 +8981,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9042,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9133,7 +9157,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9177,17 +9201,937 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
           <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3294,22 +3294,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3413,22 +3413,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,17 +3651,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,12 +3766,12 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,17 +3885,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,22 +4004,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,17 +4242,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,22 +4480,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4847,12 +4847,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,22 +5075,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,22 +5190,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,22 +5904,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6023,22 +6023,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6142,22 +6142,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6261,17 +6261,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6380,17 +6380,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,22 +6737,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,22 +7094,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7209,22 +7209,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7328,22 +7328,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7566,17 +7566,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7700,7 +7700,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7804,17 +7804,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8200,32 +8200,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8233,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8257,17 +8261,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8277,12 +8281,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8325,12 +8329,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
@@ -8352,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8401,12 +8405,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8434,32 +8438,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -8467,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8491,37 +8499,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8549,32 +8557,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8582,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8606,37 +8618,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8664,32 +8676,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8697,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8721,27 +8737,27 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8779,32 +8795,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8812,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8836,37 +8856,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8894,32 +8914,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8927,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8951,37 +8975,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9009,32 +9033,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9042,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9066,37 +9094,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9124,32 +9152,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -9157,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9181,32 +9213,32 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9239,32 +9271,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9272,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9296,32 +9332,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9354,32 +9390,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -9387,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9411,32 +9451,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9502,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9617,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9656,7 +9696,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9671,7 +9711,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9847,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9891,12 +9931,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9962,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10024,22 +10064,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10072,12 +10112,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10091,47 +10131,1197 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z83" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA83" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>82.8</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
         <is>
           <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9281,24 +9281,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9624,32 +9624,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9657,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,17 +9685,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9701,12 +9705,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9772,7 +9776,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9891,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10002,7 +10006,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10041,7 +10045,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10117,7 +10121,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10232,7 +10236,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10347,7 +10351,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10462,7 +10466,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10577,7 +10581,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10692,7 +10696,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10807,7 +10811,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10922,7 +10926,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11037,7 +11041,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11086,7 +11090,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11152,7 +11156,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11267,7 +11271,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11311,17 +11315,247 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
           <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4128,17 +4128,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4956,22 +4956,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6499,17 +6499,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7924,17 +7924,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8038,17 +8038,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,17 +8162,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,17 +8519,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8752,22 +8752,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9509,32 +9509,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9542,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,17 +9570,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9586,17 +9590,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9638,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
@@ -9661,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9710,12 +9714,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9743,32 +9747,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9776,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9800,32 +9808,32 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9858,32 +9866,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9891,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9915,17 +9927,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9935,12 +9947,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9973,32 +9985,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -10006,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10030,17 +10046,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10050,17 +10066,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10088,32 +10104,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -10121,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10145,17 +10165,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10165,17 +10185,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10318,32 +10338,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10351,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10375,37 +10399,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10581,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10620,7 +10644,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10696,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10735,7 +10759,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10811,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10926,7 +10950,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10965,7 +10989,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11041,7 +11065,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11156,7 +11180,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11271,7 +11295,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11320,12 +11344,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11410,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11430,17 +11454,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -11448,22 +11472,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11496,12 +11520,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11515,47 +11539,622 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>13/15</t>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3299,17 +3299,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,17 +3890,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,17 +5314,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5433,17 +5433,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5904,14 +5904,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6147,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6266,17 +6266,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6623,17 +6623,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6737,14 +6737,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7099,17 +7099,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7571,17 +7571,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7690,17 +7690,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,17 +7809,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,17 +8162,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8514,14 +8514,14 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8876,17 +8876,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,17 +9233,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9352,12 +9352,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9471,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,17 +9709,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10180,14 +10180,14 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
           <t>86.0</t>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10572,32 +10572,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10605,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10629,17 +10633,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10649,17 +10653,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10687,32 +10691,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10720,7 +10728,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10744,17 +10752,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10764,12 +10772,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10802,32 +10810,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10835,7 +10847,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10859,17 +10871,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10879,17 +10891,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10917,32 +10929,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10950,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10974,17 +10990,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10994,17 +11010,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11032,32 +11048,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:09</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11065,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11089,17 +11109,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11109,12 +11129,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11147,32 +11167,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -11180,7 +11204,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11204,17 +11228,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11224,17 +11248,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11262,32 +11286,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11295,7 +11323,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11319,17 +11347,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11339,17 +11367,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11525,7 +11553,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11640,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11755,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11799,17 +11827,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11837,32 +11865,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11870,7 +11902,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11894,17 +11926,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11914,17 +11946,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -11932,22 +11964,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11980,12 +12012,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11999,7 +12031,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12029,17 +12061,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12047,22 +12079,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12095,12 +12127,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12114,47 +12146,507 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>81.4</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>2/15</t>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4009,17 +4009,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4366,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,17 +5314,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7571,17 +7571,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,17 +8043,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,17 +8995,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,17 +9233,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9828,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9947,17 +9947,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10429,7 +10429,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10772,17 +10772,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11010,17 +11010,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11520,32 +11520,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11553,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11577,17 +11581,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11597,17 +11601,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11726,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -11837,7 +11841,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -11875,24 +11879,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11902,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11951,7 +11955,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -11984,32 +11988,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12017,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12041,17 +12049,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12061,17 +12069,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -12099,32 +12107,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -12132,7 +12144,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12156,17 +12168,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12176,12 +12188,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12214,32 +12226,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -12247,7 +12263,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12271,17 +12287,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12291,17 +12307,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -12329,32 +12345,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -12362,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12386,17 +12406,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12406,17 +12426,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12497,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12521,17 +12541,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -12592,7 +12612,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12636,12 +12656,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">

--- a/data/export/2026-10-17-浦东78路.xlsx
+++ b/data/export/2026-10-17-浦东78路.xlsx
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11015,12 +11015,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12069,12 +12069,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12355,12 +12355,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12431,12 +12431,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -12464,32 +12464,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12497,7 +12501,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12521,17 +12525,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12541,12 +12545,12 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12612,7 +12616,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
